--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_TURKEY_BEARDED.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_TURKEY_BEARDED.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_turkey_bearded" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_turkey_bearded" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_turkey_bearded'!$A$3:$H$17</definedName>
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.25" customWidth="1" min="1" max="1"/>
@@ -602,6 +602,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -720,6 +740,16 @@
           <t>600</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -762,6 +792,16 @@
           <t>347</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -804,6 +844,16 @@
           <t>500</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -846,6 +896,16 @@
           <t>250</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -888,6 +948,16 @@
           <t>542</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1120,6 +1190,16 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1162,6 +1242,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H17"/>
